--- a/data/journals.xlsx
+++ b/data/journals.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D460"/>
+  <dimension ref="A1:D461"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4042,18 +4042,21 @@
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Mechanics of Materials</v>
+        <v>International Journal of Energy Research</v>
       </c>
       <c r="B332">
-        <v>4.1</v>
-      </c>
-      <c r="C332">
-        <v>40.2</v>
+        <v>4.2</v>
+      </c>
+      <c r="C332" t="str">
+        <v>1.2</v>
+      </c>
+      <c r="D332" t="str">
+        <v/>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Nanoscale Research Letters</v>
+        <v>Mechanics of Materials</v>
       </c>
       <c r="B333">
         <v>4.1</v>
@@ -4064,7 +4067,7 @@
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>Sustainable Energy &amp; Fuels</v>
+        <v>Nanoscale Research Letters</v>
       </c>
       <c r="B334">
         <v>4.1</v>
@@ -4075,18 +4078,18 @@
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Iscience</v>
+        <v>Sustainable Energy &amp; Fuels</v>
       </c>
       <c r="B335">
         <v>4.1</v>
       </c>
       <c r="C335">
-        <v>15.8</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>Journal of Taibah University For Science</v>
+        <v>Iscience</v>
       </c>
       <c r="B336">
         <v>4.1</v>
@@ -4097,7 +4100,7 @@
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>Npj Microgravity</v>
+        <v>Journal of Taibah University For Science</v>
       </c>
       <c r="B337">
         <v>4.1</v>
@@ -4108,62 +4111,62 @@
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Biomass Conversion And Biorefinery</v>
+        <v>Npj Microgravity</v>
       </c>
       <c r="B338">
         <v>4.1</v>
       </c>
       <c r="C338">
-        <v>34.4</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Ecological Engineering</v>
+        <v>Biomass Conversion And Biorefinery</v>
       </c>
       <c r="B339">
         <v>4.1</v>
       </c>
       <c r="C339">
-        <v>46.4</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Journal of Electroanalytical Chemistry</v>
+        <v>Ecological Engineering</v>
       </c>
       <c r="B340">
         <v>4.1</v>
       </c>
       <c r="C340">
-        <v>37.5</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Metals And Materials International</v>
+        <v>Journal of Electroanalytical Chemistry</v>
       </c>
       <c r="B341">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="C341">
-        <v>41.1</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Aiche Journal</v>
+        <v>Metals And Materials International</v>
       </c>
       <c r="B342">
         <v>4</v>
       </c>
       <c r="C342">
-        <v>35.5</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Process Biochemistry</v>
+        <v>Aiche Journal</v>
       </c>
       <c r="B343">
         <v>4</v>
@@ -4174,29 +4177,29 @@
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Catalysts</v>
+        <v>Process Biochemistry</v>
       </c>
       <c r="B344">
         <v>4</v>
       </c>
       <c r="C344">
-        <v>44.6</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Bioconjugate Chemistry</v>
+        <v>Catalysts</v>
       </c>
       <c r="B345">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="C345">
-        <v>36.6</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Langmuir</v>
+        <v>Bioconjugate Chemistry</v>
       </c>
       <c r="B346">
         <v>3.9</v>
@@ -4207,18 +4210,18 @@
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Heritage Science</v>
+        <v>Langmuir</v>
       </c>
       <c r="B347">
         <v>3.9</v>
       </c>
       <c r="C347">
-        <v>41.8</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>International Journal of Damage Mechanics</v>
+        <v>Heritage Science</v>
       </c>
       <c r="B348">
         <v>3.9</v>
@@ -4229,7 +4232,7 @@
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Journal of Materials Science</v>
+        <v>International Journal of Damage Mechanics</v>
       </c>
       <c r="B349">
         <v>3.9</v>
@@ -4240,7 +4243,7 @@
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Materials And Structures</v>
+        <v>Journal of Materials Science</v>
       </c>
       <c r="B350">
         <v>3.9</v>
@@ -4251,7 +4254,7 @@
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Reviews On Advanced Materials Science</v>
+        <v>Materials And Structures</v>
       </c>
       <c r="B351">
         <v>3.9</v>
@@ -4262,7 +4265,7 @@
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Vacuum</v>
+        <v>Reviews On Advanced Materials Science</v>
       </c>
       <c r="B352">
         <v>3.9</v>
@@ -4273,18 +4276,18 @@
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Gigascience</v>
+        <v>Vacuum</v>
       </c>
       <c r="B353">
         <v>3.9</v>
       </c>
       <c r="C353">
-        <v>18</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Scientific Reports</v>
+        <v>Gigascience</v>
       </c>
       <c r="B354">
         <v>3.9</v>
@@ -4295,18 +4298,18 @@
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Chemical Engineering And Processing-Process Intensification</v>
+        <v>Scientific Reports</v>
       </c>
       <c r="B355">
         <v>3.9</v>
       </c>
       <c r="C355">
-        <v>36.6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Chemical Engineering Research &amp; Design</v>
+        <v>Chemical Engineering And Processing-Process Intensification</v>
       </c>
       <c r="B356">
         <v>3.9</v>
@@ -4317,7 +4320,7 @@
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Computers &amp; Chemical Engineering</v>
+        <v>Chemical Engineering Research &amp; Design</v>
       </c>
       <c r="B357">
         <v>3.9</v>
@@ -4328,7 +4331,7 @@
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Industrial &amp; Engineering Chemistry Research</v>
+        <v>Computers &amp; Chemical Engineering</v>
       </c>
       <c r="B358">
         <v>3.9</v>
@@ -4339,7 +4342,7 @@
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Journal of Process Control</v>
+        <v>Industrial &amp; Engineering Chemistry Research</v>
       </c>
       <c r="B359">
         <v>3.9</v>
@@ -4350,40 +4353,40 @@
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Chemcatchem</v>
+        <v>Journal of Process Control</v>
       </c>
       <c r="B360">
         <v>3.9</v>
       </c>
       <c r="C360">
-        <v>45.1</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>Clean Technologies And Environmental Policy</v>
+        <v>Chemcatchem</v>
       </c>
       <c r="B361">
         <v>3.9</v>
       </c>
       <c r="C361">
-        <v>48.8</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>Bulletin of The Chemical Society of Japan</v>
+        <v>Clean Technologies And Environmental Policy</v>
       </c>
       <c r="B362">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="C362">
-        <v>37.9</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Chemical Research In Toxicology</v>
+        <v>Bulletin of The Chemical Society of Japan</v>
       </c>
       <c r="B363">
         <v>3.8</v>
@@ -4394,7 +4397,7 @@
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Journal of Pharmaceutical Sciences</v>
+        <v>Chemical Research In Toxicology</v>
       </c>
       <c r="B364">
         <v>3.8</v>
@@ -4405,7 +4408,7 @@
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Molecular Diversity</v>
+        <v>Journal of Pharmaceutical Sciences</v>
       </c>
       <c r="B365">
         <v>3.8</v>
@@ -4416,18 +4419,18 @@
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>Advances In Manufacturing</v>
+        <v>Molecular Diversity</v>
       </c>
       <c r="B366">
         <v>3.8</v>
       </c>
       <c r="C366">
-        <v>43.9</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Smart Materials And Structures</v>
+        <v>Advances In Manufacturing</v>
       </c>
       <c r="B367">
         <v>3.8</v>
@@ -4438,29 +4441,29 @@
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Biochemical Engineering Journal</v>
+        <v>Smart Materials And Structures</v>
       </c>
       <c r="B368">
         <v>3.8</v>
       </c>
       <c r="C368">
-        <v>39.5</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Cold Regions Science And Technology</v>
+        <v>Biochemical Engineering Journal</v>
       </c>
       <c r="B369">
         <v>3.8</v>
       </c>
       <c r="C369">
-        <v>51.2</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Environmental Geochemistry And Health</v>
+        <v>Cold Regions Science And Technology</v>
       </c>
       <c r="B370">
         <v>3.8</v>
@@ -4471,29 +4474,29 @@
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Chemistry-A European Journal</v>
+        <v>Environmental Geochemistry And Health</v>
       </c>
       <c r="B371">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="C371">
-        <v>39.5</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>Journal of Adhesion Science And Technology</v>
+        <v>Chemistry-A European Journal</v>
       </c>
       <c r="B372">
         <v>3.7</v>
       </c>
       <c r="C372">
-        <v>45</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Materials Technology</v>
+        <v>Journal of Adhesion Science And Technology</v>
       </c>
       <c r="B373">
         <v>3.7</v>
@@ -4504,7 +4507,7 @@
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>Physical Review B</v>
+        <v>Materials Technology</v>
       </c>
       <c r="B374">
         <v>3.7</v>
@@ -4515,7 +4518,7 @@
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Science And Technology of Welding And Joining</v>
+        <v>Physical Review B</v>
       </c>
       <c r="B375">
         <v>3.7</v>
@@ -4526,73 +4529,73 @@
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Philosophical Transactions of The Royal Society A-Mathematical Physical And Engineering Sciences</v>
+        <v>Science And Technology of Welding And Joining</v>
       </c>
       <c r="B376">
         <v>3.7</v>
       </c>
       <c r="C376">
-        <v>20.2</v>
+        <v>45</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Chinese Journal of Chemical Engineering</v>
+        <v>Philosophical Transactions of The Royal Society A-Mathematical Physical And Engineering Sciences</v>
       </c>
       <c r="B377">
         <v>3.7</v>
       </c>
       <c r="C377">
-        <v>40.1</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Journal of Terramechanics</v>
+        <v>Chinese Journal of Chemical Engineering</v>
       </c>
       <c r="B378">
         <v>3.7</v>
       </c>
       <c r="C378">
-        <v>53.6</v>
+        <v>40.1</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Classical And Quantum Gravity</v>
+        <v>Journal of Terramechanics</v>
       </c>
       <c r="B379">
         <v>3.7</v>
       </c>
       <c r="C379">
-        <v>23.2</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Chemosensors</v>
+        <v>Classical And Quantum Gravity</v>
       </c>
       <c r="B380">
         <v>3.7</v>
       </c>
       <c r="C380">
-        <v>42</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Archiv Der Pharmazie</v>
+        <v>Chemosensors</v>
       </c>
       <c r="B381">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="C381">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Iucrj</v>
+        <v>Archiv Der Pharmazie</v>
       </c>
       <c r="B382">
         <v>3.6</v>
@@ -4603,18 +4606,18 @@
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>International Journal For Numerical And Analytical Methods In Geomechanics</v>
+        <v>Iucrj</v>
       </c>
       <c r="B383">
         <v>3.6</v>
       </c>
       <c r="C383">
-        <v>45.9</v>
+        <v>40</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>International Journal of Concrete Structures And Materials</v>
+        <v>International Journal For Numerical And Analytical Methods In Geomechanics</v>
       </c>
       <c r="B384">
         <v>3.6</v>
@@ -4625,7 +4628,7 @@
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>International Journal of Mechanics And Materials In Design</v>
+        <v>International Journal of Concrete Structures And Materials</v>
       </c>
       <c r="B385">
         <v>3.6</v>
@@ -4636,7 +4639,7 @@
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Membranes</v>
+        <v>International Journal of Mechanics And Materials In Design</v>
       </c>
       <c r="B386">
         <v>3.6</v>
@@ -4647,7 +4650,7 @@
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Rapid Prototyping Journal</v>
+        <v>Membranes</v>
       </c>
       <c r="B387">
         <v>3.6</v>
@@ -4658,18 +4661,18 @@
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Heliyon</v>
+        <v>Rapid Prototyping Journal</v>
       </c>
       <c r="B388">
         <v>3.6</v>
       </c>
       <c r="C388">
-        <v>21</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Journal of King Saud University Science</v>
+        <v>Heliyon</v>
       </c>
       <c r="B389">
         <v>3.6</v>
@@ -4680,51 +4683,51 @@
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Bioprocess And Biosystems Engineering</v>
+        <v>Journal of King Saud University Science</v>
       </c>
       <c r="B390">
         <v>3.6</v>
       </c>
       <c r="C390">
-        <v>41.2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>Stochastic Environmental Research And Risk Assessment</v>
+        <v>Bioprocess And Biosystems Engineering</v>
       </c>
       <c r="B391">
         <v>3.6</v>
       </c>
       <c r="C391">
-        <v>56</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Research On Chemical Intermediates</v>
+        <v>Stochastic Environmental Research And Risk Assessment</v>
       </c>
       <c r="B392">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="C392">
-        <v>41.2</v>
+        <v>56</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>International Journal of Adhesion And Adhesives</v>
+        <v>Research On Chemical Intermediates</v>
       </c>
       <c r="B393">
         <v>3.5</v>
       </c>
       <c r="C393">
-        <v>47.4</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Journal of Non-Crystalline Solids</v>
+        <v>International Journal of Adhesion And Adhesives</v>
       </c>
       <c r="B394">
         <v>3.5</v>
@@ -4735,29 +4738,29 @@
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Journal of The Royal Society Interface</v>
+        <v>Journal of Non-Crystalline Solids</v>
       </c>
       <c r="B395">
         <v>3.5</v>
       </c>
       <c r="C395">
-        <v>22.4</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Journal of Solid State Chemistry</v>
+        <v>Journal of The Royal Society Interface</v>
       </c>
       <c r="B396">
         <v>3.5</v>
       </c>
       <c r="C396">
-        <v>47.3</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Surface Innovations</v>
+        <v>Journal of Solid State Chemistry</v>
       </c>
       <c r="B397">
         <v>3.5</v>
@@ -4768,7 +4771,7 @@
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Thermochimica Acta</v>
+        <v>Surface Innovations</v>
       </c>
       <c r="B398">
         <v>3.5</v>
@@ -4779,40 +4782,40 @@
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Physics Today</v>
+        <v>Thermochimica Acta</v>
       </c>
       <c r="B399">
         <v>3.5</v>
       </c>
       <c r="C399">
-        <v>24.1</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Chemelectrochem</v>
+        <v>Physics Today</v>
       </c>
       <c r="B400">
         <v>3.5</v>
       </c>
       <c r="C400">
-        <v>44.3</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Crystal Growth &amp; Design</v>
+        <v>Chemelectrochem</v>
       </c>
       <c r="B401">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="C401">
-        <v>41.6</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Journal of The Indian Chemical Society</v>
+        <v>Crystal Growth &amp; Design</v>
       </c>
       <c r="B402">
         <v>3.4</v>
@@ -4823,18 +4826,18 @@
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Journal of Information Display</v>
+        <v>Journal of The Indian Chemical Society</v>
       </c>
       <c r="B403">
         <v>3.4</v>
       </c>
       <c r="C403">
-        <v>48.5</v>
+        <v>41.6</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Physical Review Materials</v>
+        <v>Journal of Information Display</v>
       </c>
       <c r="B404">
         <v>3.4</v>
@@ -4845,51 +4848,51 @@
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Food And Bioproducts Processing</v>
+        <v>Physical Review Materials</v>
       </c>
       <c r="B405">
         <v>3.4</v>
       </c>
       <c r="C405">
-        <v>44</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Physics-Uspekhi</v>
+        <v>Food And Bioproducts Processing</v>
       </c>
       <c r="B406">
         <v>3.4</v>
       </c>
       <c r="C406">
-        <v>25</v>
+        <v>44</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Chemistry-An Asian Journal</v>
+        <v>Physics-Uspekhi</v>
       </c>
       <c r="B407">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="C407">
-        <v>42.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Advanced Engineering Materials</v>
+        <v>Chemistry-An Asian Journal</v>
       </c>
       <c r="B408">
         <v>3.3</v>
       </c>
       <c r="C408">
-        <v>49.1</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Computational Materials Science</v>
+        <v>Advanced Engineering Materials</v>
       </c>
       <c r="B409">
         <v>3.3</v>
@@ -4900,7 +4903,7 @@
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Fire Safety Journal</v>
+        <v>Computational Materials Science</v>
       </c>
       <c r="B410">
         <v>3.3</v>
@@ -4911,7 +4914,7 @@
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Geosynthetics International</v>
+        <v>Fire Safety Journal</v>
       </c>
       <c r="B411">
         <v>3.3</v>
@@ -4922,7 +4925,7 @@
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Journal of Cultural Heritage</v>
+        <v>Geosynthetics International</v>
       </c>
       <c r="B412">
         <v>3.3</v>
@@ -4933,7 +4936,7 @@
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Nano Futures</v>
+        <v>Journal of Cultural Heritage</v>
       </c>
       <c r="B413">
         <v>3.3</v>
@@ -4944,7 +4947,7 @@
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Nanomaterials And Nanotechnology</v>
+        <v>Nano Futures</v>
       </c>
       <c r="B414">
         <v>3.3</v>
@@ -4955,7 +4958,7 @@
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Silicon</v>
+        <v>Nanomaterials And Nanotechnology</v>
       </c>
       <c r="B415">
         <v>3.3</v>
@@ -4966,29 +4969,29 @@
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Tribology Letters</v>
+        <v>Silicon</v>
       </c>
       <c r="B416">
         <v>3.3</v>
       </c>
       <c r="C416">
-        <v>45.2</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Radiation Physics And Chemistry</v>
+        <v>Tribology Letters</v>
       </c>
       <c r="B417">
         <v>3.3</v>
       </c>
       <c r="C417">
-        <v>48.9</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Solid State Ionics</v>
+        <v>Radiation Physics And Chemistry</v>
       </c>
       <c r="B418">
         <v>3.3</v>
@@ -4999,7 +5002,7 @@
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Solid State Sciences</v>
+        <v>Solid State Ionics</v>
       </c>
       <c r="B419">
         <v>3.3</v>
@@ -5010,51 +5013,51 @@
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Water Reuse</v>
+        <v>Solid State Sciences</v>
       </c>
       <c r="B420">
         <v>3.3</v>
       </c>
       <c r="C420">
-        <v>57.2</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Contemporary Physics</v>
+        <v>Water Reuse</v>
       </c>
       <c r="B421">
         <v>3.3</v>
       </c>
       <c r="C421">
-        <v>25.9</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Journal of The Electrochemical Society</v>
+        <v>Contemporary Physics</v>
       </c>
       <c r="B422">
         <v>3.3</v>
       </c>
       <c r="C422">
-        <v>46.6</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Journal of Physical And Chemical Reference Data</v>
+        <v>Journal of The Electrochemical Society</v>
       </c>
       <c r="B423">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="C423">
-        <v>42.9</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Korean Journal of Chemical Engineering</v>
+        <v>Journal of Physical And Chemical Reference Data</v>
       </c>
       <c r="B424">
         <v>3.2</v>
@@ -5065,18 +5068,18 @@
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Advances In Nano Research</v>
+        <v>Korean Journal of Chemical Engineering</v>
       </c>
       <c r="B425">
         <v>3.2</v>
       </c>
       <c r="C425">
-        <v>51.3</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Fatigue &amp; Fracture of Engineering Materials &amp; Structures</v>
+        <v>Advances In Nano Research</v>
       </c>
       <c r="B426">
         <v>3.2</v>
@@ -5087,7 +5090,7 @@
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Flexible And Printed Electronics</v>
+        <v>Fatigue &amp; Fracture of Engineering Materials &amp; Structures</v>
       </c>
       <c r="B427">
         <v>3.2</v>
@@ -5098,7 +5101,7 @@
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Journal of Nuclear Materials</v>
+        <v>Flexible And Printed Electronics</v>
       </c>
       <c r="B428">
         <v>3.2</v>
@@ -5109,7 +5112,7 @@
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Journal of Physical Chemistry C</v>
+        <v>Journal of Nuclear Materials</v>
       </c>
       <c r="B429">
         <v>3.2</v>
@@ -5120,7 +5123,7 @@
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Journal of Porous Materials</v>
+        <v>Journal of Physical Chemistry C</v>
       </c>
       <c r="B430">
         <v>3.2</v>
@@ -5131,7 +5134,7 @@
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Kona Powder And Particle Journal</v>
+        <v>Journal of Porous Materials</v>
       </c>
       <c r="B431">
         <v>3.2</v>
@@ -5142,7 +5145,7 @@
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Materials</v>
+        <v>Kona Powder And Particle Journal</v>
       </c>
       <c r="B432">
         <v>3.2</v>
@@ -5153,7 +5156,7 @@
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Molecular Systems Design &amp; Engineering</v>
+        <v>Materials</v>
       </c>
       <c r="B433">
         <v>3.2</v>
@@ -5164,18 +5167,18 @@
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Adsorption Science &amp; Technology</v>
+        <v>Molecular Systems Design &amp; Engineering</v>
       </c>
       <c r="B434">
         <v>3.2</v>
       </c>
       <c r="C434">
-        <v>45.7</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Journal of Microencapsulation</v>
+        <v>Adsorption Science &amp; Technology</v>
       </c>
       <c r="B435">
         <v>3.2</v>
@@ -5186,7 +5189,7 @@
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Polymer Engineering And Science</v>
+        <v>Journal of Microencapsulation</v>
       </c>
       <c r="B436">
         <v>3.2</v>
@@ -5197,18 +5200,18 @@
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Photochemical &amp; Photobiological Sciences</v>
+        <v>Polymer Engineering And Science</v>
       </c>
       <c r="B437">
         <v>3.2</v>
       </c>
       <c r="C437">
-        <v>51.1</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Zeitschrift Fur Physikalische Chemie-International Journal of Research In Physical Chemistry &amp; Chemical Physics</v>
+        <v>Photochemical &amp; Photobiological Sciences</v>
       </c>
       <c r="B438">
         <v>3.2</v>
@@ -5219,40 +5222,40 @@
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Environmental Science-Water Research &amp; Technology</v>
+        <v>Zeitschrift Fur Physikalische Chemie-International Journal of Research In Physical Chemistry &amp; Chemical Physics</v>
       </c>
       <c r="B439">
         <v>3.2</v>
       </c>
       <c r="C439">
-        <v>58.4</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Corrosion Reviews</v>
+        <v>Environmental Science-Water Research &amp; Technology</v>
       </c>
       <c r="B440">
         <v>3.2</v>
       </c>
       <c r="C440">
-        <v>48.9</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Chemistryopen</v>
+        <v>Corrosion Reviews</v>
       </c>
       <c r="B441">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="C441">
-        <v>43.7</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Reaction Chemistry &amp; Engineering</v>
+        <v>Chemistryopen</v>
       </c>
       <c r="B442">
         <v>3.1</v>
@@ -5263,18 +5266,18 @@
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Current Applied Physics</v>
+        <v>Reaction Chemistry &amp; Engineering</v>
       </c>
       <c r="B443">
         <v>3.1</v>
       </c>
       <c r="C443">
-        <v>53.3</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Metallurgical And Materials Transactions B-Process Metallurgy And Materials Processing Science</v>
+        <v>Current Applied Physics</v>
       </c>
       <c r="B444">
         <v>3.1</v>
@@ -5285,7 +5288,7 @@
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Optical Materials Express</v>
+        <v>Metallurgical And Materials Transactions B-Process Metallurgy And Materials Processing Science</v>
       </c>
       <c r="B445">
         <v>3.1</v>
@@ -5296,7 +5299,7 @@
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Recent Patents On Nanotechnology</v>
+        <v>Optical Materials Express</v>
       </c>
       <c r="B446">
         <v>3.1</v>
@@ -5307,29 +5310,29 @@
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Adsorption-Journal of The International Adsorption Society</v>
+        <v>Recent Patents On Nanotechnology</v>
       </c>
       <c r="B447">
         <v>3.1</v>
       </c>
       <c r="C447">
-        <v>48.6</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Chemical Physics Letters</v>
+        <v>Adsorption-Journal of The International Adsorption Society</v>
       </c>
       <c r="B448">
         <v>3.1</v>
       </c>
       <c r="C448">
-        <v>55.9</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Faraday Discussions</v>
+        <v>Chemical Physics Letters</v>
       </c>
       <c r="B449">
         <v>3.1</v>
@@ -5340,7 +5343,7 @@
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>International Reviews In Physical Chemistry</v>
+        <v>Faraday Discussions</v>
       </c>
       <c r="B450">
         <v>3.1</v>
@@ -5351,7 +5354,7 @@
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Journal of Chemical Physics</v>
+        <v>International Reviews In Physical Chemistry</v>
       </c>
       <c r="B451">
         <v>3.1</v>
@@ -5362,7 +5365,7 @@
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Journal of Fluorescence</v>
+        <v>Journal of Chemical Physics</v>
       </c>
       <c r="B452">
         <v>3.1</v>
@@ -5373,7 +5376,7 @@
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Journal of Thermal Analysis And Calorimetry</v>
+        <v>Journal of Fluorescence</v>
       </c>
       <c r="B453">
         <v>3.1</v>
@@ -5384,7 +5387,7 @@
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Vibrational Spectroscopy</v>
+        <v>Journal of Thermal Analysis And Calorimetry</v>
       </c>
       <c r="B454">
         <v>3.1</v>
@@ -5395,40 +5398,40 @@
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Physica A-Statistical Mechanics And Its Applications</v>
+        <v>Vibrational Spectroscopy</v>
       </c>
       <c r="B455">
         <v>3.1</v>
       </c>
       <c r="C455">
-        <v>27.6</v>
+        <v>55.9</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Fuel Cells</v>
+        <v>Physica A-Statistical Mechanics And Its Applications</v>
       </c>
       <c r="B456">
         <v>3.1</v>
       </c>
       <c r="C456">
-        <v>51.1</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Russian Chemical Bulletin</v>
-      </c>
-      <c r="B457" t="str">
-        <v>-</v>
-      </c>
-      <c r="C457" t="str">
-        <v>-</v>
+        <v>Fuel Cells</v>
+      </c>
+      <c r="B457">
+        <v>3.1</v>
+      </c>
+      <c r="C457">
+        <v>51.1</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>Mechanics of Advanced Materials And Structures</v>
+        <v>Russian Chemical Bulletin</v>
       </c>
       <c r="B458" t="str">
         <v>-</v>
@@ -5439,7 +5442,7 @@
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>Transactions of Famena</v>
+        <v>Mechanics of Advanced Materials And Structures</v>
       </c>
       <c r="B459" t="str">
         <v>-</v>
@@ -5450,7 +5453,7 @@
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Applied Catalysis O: Open</v>
+        <v>Transactions of Famena</v>
       </c>
       <c r="B460" t="str">
         <v>-</v>
@@ -5459,9 +5462,20 @@
         <v>-</v>
       </c>
     </row>
+    <row r="461">
+      <c r="A461" t="str">
+        <v>Applied Catalysis O: Open</v>
+      </c>
+      <c r="B461" t="str">
+        <v>-</v>
+      </c>
+      <c r="C461" t="str">
+        <v>-</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D460"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D461"/>
   </ignoredErrors>
 </worksheet>
 </file>